--- a/src/app/assets/invData.xlsx
+++ b/src/app/assets/invData.xlsx
@@ -20919,7 +20919,7 @@
         <v>Klub</v>
       </c>
       <c r="B1482" t="str">
-        <v>64 Gb</v>
+        <v>32 Gb</v>
       </c>
     </row>
     <row r="1483">

--- a/src/app/assets/invData.xlsx
+++ b/src/app/assets/invData.xlsx
@@ -20921,6 +20921,12 @@
       <c r="B1482" t="str">
         <v>32 Gb</v>
       </c>
+      <c r="D1482" t="str">
+        <v>EMMC</v>
+      </c>
+      <c r="E1482" t="str">
+        <v>180 TL</v>
+      </c>
     </row>
     <row r="1483">
       <c r="A1483" t="str">
